--- a/data_out/country_spreadsheets/Portugal.xlsx
+++ b/data_out/country_spreadsheets/Portugal.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:AN25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,87 +461,172 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Median drought days per year</t>
+          <t>Median drought-warning-days</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Maximum recorded drought days per year</t>
+          <t>Maximum recorded drought-warning-days</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>most severe drought year</t>
+          <t>Year of maximum drought-warning-days</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2012</t>
+          <t>Warning days 2012</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2013</t>
+          <t>Warning days 2013</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2014</t>
+          <t>Warning days 2014</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2015</t>
+          <t>Warning days 2015</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2016</t>
+          <t>Warning days 2016</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2017</t>
+          <t>Warning days 2017</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2018</t>
+          <t>Warning days 2018</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2019</t>
+          <t>Warning days 2019</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2020</t>
+          <t>Warning days 2020</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2021</t>
+          <t>Warning days 2021</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2022</t>
+          <t>Warning days 2022</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2023</t>
+          <t>Warning days 2023</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2024</t>
+          <t>Warning days 2024</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2025</t>
+          <t>Warning days 2025</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Median drought-alert-days</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Maximum recorded drought-alert-days</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Year of maximum drought-alert-days</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2012</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2013</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2014</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2015</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2016</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2017</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2018</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2019</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2020</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2021</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2022</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2023</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2024</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2025</t>
         </is>
       </c>
     </row>
@@ -621,6 +706,57 @@
       <c r="W2" t="n">
         <v>62.03</v>
       </c>
+      <c r="X2" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>145.96</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>34.06</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>66.69</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>85.05</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>280.13</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>58.22</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>25.78</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>218.29</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>26.97</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>62.03</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -698,6 +834,57 @@
       <c r="W3" t="n">
         <v>29.84</v>
       </c>
+      <c r="X3" t="n">
+        <v>9.74</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>24.02</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>104.28</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>27.37</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>70.81999999999999</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>206.38</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>52.03</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>25.78</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>53.63</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>27.11</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>160.17</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>59.03</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>29.84</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -775,6 +962,57 @@
       <c r="W4" t="n">
         <v>21.01</v>
       </c>
+      <c r="X4" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>32.25</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>120.1</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>12.49</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>44.04</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>61.16</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>251.6</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>58.82</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>45.01</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>15.91</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>234.65</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>20.56</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>21.01</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -852,6 +1090,57 @@
       <c r="W5" t="n">
         <v>37.92</v>
       </c>
+      <c r="X5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>20.79</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2017</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>51.68</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>71.84</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>33.31</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>221.19</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>57.79</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>66.17</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>18.28</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>169.23</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>48.14</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>37.92</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -929,6 +1218,57 @@
       <c r="W6" t="n">
         <v>49.41</v>
       </c>
+      <c r="X6" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>76.64</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>195.55</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>34.35</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>12.01</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>58.98</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>53.83</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>153.14</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>77.37</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>40.23</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>46.99</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>39.06</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>245.3</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>33.48</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>49.41</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1006,6 +1346,57 @@
       <c r="W7" t="n">
         <v>36.23</v>
       </c>
+      <c r="X7" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>35.12</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>141.28</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>77.78</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>137.75</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>25.66</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>173.89</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>56.37</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>28.83</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>25.77</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>183.19</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>33.91</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>36.23</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1083,6 +1474,57 @@
       <c r="W8" t="n">
         <v>21.96</v>
       </c>
+      <c r="X8" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>252.42</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>42.42</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>121.98</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>14.59</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>194.33</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>80.33</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>50.81</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>8.81</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>29.85</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>283.86</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>35.02</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>21.96</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1160,6 +1602,57 @@
       <c r="W9" t="n">
         <v>31.83</v>
       </c>
+      <c r="X9" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>116.22</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>262.61</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>15.07</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>90.98999999999999</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>29.92</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>196.08</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>86.48999999999999</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>65.59</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>28.69</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>284.18</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>31.83</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1237,6 +1730,57 @@
       <c r="W10" t="n">
         <v>34.13</v>
       </c>
+      <c r="X10" t="n">
+        <v>19.37</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>177.07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>22.94</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>108.01</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>24.49</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>190.28</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>78.72</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>131.72</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>122.63</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>28.54</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>34.13</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1314,6 +1858,57 @@
       <c r="W11" t="n">
         <v>19.12</v>
       </c>
+      <c r="X11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>140.62</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>51.49</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>39.77</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>151.82</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>119.74</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>19.86</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>29.05</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>232.91</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>108.25</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>19.12</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1391,6 +1986,57 @@
       <c r="W12" t="n">
         <v>42.76</v>
       </c>
+      <c r="X12" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>22.48</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>138.28</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>15.54</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>180.95</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>65.55</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>37.72</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>24.58</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>246.65</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>36.96</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>42.76</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1468,6 +2114,57 @@
       <c r="W13" t="n">
         <v>15.73</v>
       </c>
+      <c r="X13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>48.37</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>191.1</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>43.41</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>43.74</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>289.8</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>67.92</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>229.37</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>21.39</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>15.73</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1545,6 +2242,57 @@
       <c r="W14" t="n">
         <v>25.48</v>
       </c>
+      <c r="X14" t="n">
+        <v>8.34</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>49.85</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>133.8</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>120.18</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>42.67</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>214.58</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>53.04</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>65.36</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>216.09</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>81</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>25.48</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1622,6 +2370,57 @@
       <c r="W15" t="n">
         <v>19.46</v>
       </c>
+      <c r="X15" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>45.82</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>223.52</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>32.31</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>84.7</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>58.96</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>275.62</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>109.19</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>121.88</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>19.11</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>249.41</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>13.36</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>19.46</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1699,6 +2498,57 @@
       <c r="W16" t="n">
         <v>30.17</v>
       </c>
+      <c r="X16" t="n">
+        <v>13.48</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>95.95999999999999</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>217.02</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>13.54</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>44.83</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>93.98</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>68.12</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>82.48</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>20.22</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>170.91</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>59.36</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>30.17</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1776,6 +2626,57 @@
       <c r="W17" t="n">
         <v>13.07</v>
       </c>
+      <c r="X17" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>66.83</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>105.45</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>161.88</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>36.38</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>185.49</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>70.37</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>52.04</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>241.57</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>63.96</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>13.07</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1853,6 +2754,57 @@
       <c r="W18" t="n">
         <v>25.44</v>
       </c>
+      <c r="X18" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>102.66</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>207.42</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>95.45999999999999</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>180.67</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>188.98</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>41.72</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>25.44</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -1930,6 +2882,57 @@
       <c r="W19" t="n">
         <v>33.98</v>
       </c>
+      <c r="X19" t="n">
+        <v>14.74</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>76.29000000000001</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>123.68</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>56.27</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>27.66</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>124.4</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>83.04000000000001</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>228.55</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>28.16</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>59.38</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>247.3</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>104.19</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>17.29</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>33.98</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -2007,6 +3010,57 @@
       <c r="W20" t="n">
         <v>48.34</v>
       </c>
+      <c r="X20" t="n">
+        <v>27.22</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>120.27</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>8.93</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>47.38</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>15.96</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>60.12</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>188.48</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>252.61</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>193.36</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>20.68</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>48.34</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -2084,6 +3138,57 @@
       <c r="W21" t="n">
         <v>48.53</v>
       </c>
+      <c r="X21" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>85.37</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>134.64</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>10.13</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>35.89</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>45.67</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>92.93000000000001</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>129.7</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>42.38</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>42.46</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>231.65</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>166.76</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>18.72</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>48.53</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -2161,6 +3266,57 @@
       <c r="W22" t="n">
         <v>23.51</v>
       </c>
+      <c r="X22" t="n">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>81.26000000000001</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>105.37</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>24.14</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>36.27</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>195.08</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>77.79000000000001</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>196.47</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>49.46</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>254.84</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>26.96</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>23.51</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -2238,6 +3394,57 @@
       <c r="W23" t="n">
         <v>38.45</v>
       </c>
+      <c r="X23" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>104.54</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>190.08</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>184.12</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>70.78</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>113.16</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>21.84</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>205.42</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>58.61</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>38.45</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -2315,6 +3522,57 @@
       <c r="W24" t="n">
         <v>55.98</v>
       </c>
+      <c r="X24" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>104.13</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>207.03</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>50.34</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>25.88</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>123.48</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>65.06</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>135.42</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>17.18</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>194.36</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>116.08</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>21.69</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>55.98</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -2390,6 +3648,57 @@
         <v>1.11</v>
       </c>
       <c r="W25" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>17.44</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>188.26</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>19.94</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>76.93000000000001</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>30.66</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>45.51</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>22.41</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AN25" t="n">
         <v>0.31</v>
       </c>
     </row>
